--- a/curation/draft/package18/R18_BC_DSS_BrCa_TAUG_2.xlsx
+++ b/curation/draft/package18/R18_BC_DSS_BrCa_TAUG_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package18\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCD810C-50D3-4BA1-9FAF-3702EFF3A660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801E0AAC-F3D5-4645-B306-DEF33474D364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{9C2B54C0-060B-496F-B408-7D0F2041239C}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" xr2:uid="{9C2B54C0-060B-496F-B408-7D0F2041239C}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_BrCa" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2628" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2628" uniqueCount="192">
   <si>
     <t>package_date</t>
   </si>
@@ -617,13 +617,16 @@
   </si>
   <si>
     <t>SIMPLE MASTECTOMY;LYMPH NODE DISSECTION;TOTAL MASTECTOMY;MODIFIED RADICAL MASTECTOMY;RADICAL MASTECTOMY;LUMPECTOMY</t>
+  </si>
+  <si>
+    <t>CTSCANPELVIS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1135,20 +1138,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02DBC567-A798-4813-83E1-012FB631D130}">
   <dimension ref="A1:R42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" customWidth="1"/>
-    <col min="6" max="6" width="33.140625" customWidth="1"/>
-    <col min="7" max="7" width="24.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.29296875" customWidth="1"/>
+    <col min="6" max="6" width="33.1171875" customWidth="1"/>
+    <col min="7" max="7" width="24.87890625" customWidth="1"/>
     <col min="9" max="9" width="45" customWidth="1"/>
     <col min="10" max="12" width="9" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="32.7109375" customWidth="1"/>
-    <col min="17" max="17" width="42.28515625" customWidth="1"/>
-    <col min="18" max="18" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.41015625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32.703125" customWidth="1"/>
+    <col min="17" max="17" width="42.29296875" customWidth="1"/>
+    <col min="18" max="18" width="17.703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="3" customFormat="1" ht="14.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1204,7 +1207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="15" customFormat="1">
       <c r="A2" s="11" t="s">
         <v>31</v>
       </c>
@@ -1235,7 +1238,7 @@
       <c r="P2" s="11"/>
       <c r="Q2" s="12"/>
     </row>
-    <row r="3" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A3" s="11" t="s">
         <v>31</v>
       </c>
@@ -1280,7 +1283,7 @@
       </c>
       <c r="Q3" s="12"/>
     </row>
-    <row r="4" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A4" s="11" t="s">
         <v>31</v>
       </c>
@@ -1325,7 +1328,7 @@
       </c>
       <c r="Q4" s="12"/>
     </row>
-    <row r="5" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A5" s="11" t="s">
         <v>31</v>
       </c>
@@ -1370,7 +1373,7 @@
       </c>
       <c r="Q5" s="12"/>
     </row>
-    <row r="6" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A6" s="11" t="s">
         <v>31</v>
       </c>
@@ -1415,7 +1418,7 @@
       </c>
       <c r="Q6" s="12"/>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1462,7 +1465,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A8" s="11" t="s">
         <v>31</v>
       </c>
@@ -1507,7 +1510,7 @@
       </c>
       <c r="Q8" s="12"/>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A9" s="11" t="s">
         <v>31</v>
       </c>
@@ -1554,7 +1557,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A10" s="11" t="s">
         <v>31</v>
       </c>
@@ -1599,7 +1602,7 @@
       </c>
       <c r="Q10" s="12"/>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A11" s="11" t="s">
         <v>31</v>
       </c>
@@ -1644,7 +1647,7 @@
       </c>
       <c r="Q11" s="12"/>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
@@ -1691,7 +1694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A13" s="11" t="s">
         <v>31</v>
       </c>
@@ -1736,7 +1739,7 @@
       </c>
       <c r="Q13" s="12"/>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A14" s="11" t="s">
         <v>31</v>
       </c>
@@ -1781,7 +1784,7 @@
       </c>
       <c r="Q14" s="12"/>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A15" s="11" t="s">
         <v>31</v>
       </c>
@@ -1826,7 +1829,7 @@
       </c>
       <c r="Q15" s="12"/>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="28.7">
       <c r="A16" s="11" t="s">
         <v>31</v>
       </c>
@@ -1871,7 +1874,7 @@
       </c>
       <c r="Q16" s="12"/>
     </row>
-    <row r="17" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A17" s="11" t="s">
         <v>31</v>
       </c>
@@ -1918,7 +1921,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A18" s="11" t="s">
         <v>31</v>
       </c>
@@ -1965,7 +1968,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A19" s="11" t="s">
         <v>31</v>
       </c>
@@ -2012,7 +2015,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A20" s="11" t="s">
         <v>31</v>
       </c>
@@ -2057,7 +2060,7 @@
       </c>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A21" s="11" t="s">
         <v>31</v>
       </c>
@@ -2102,7 +2105,7 @@
       </c>
       <c r="Q21" s="12"/>
     </row>
-    <row r="22" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A22" s="11" t="s">
         <v>31</v>
       </c>
@@ -2149,7 +2152,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A23" s="11" t="s">
         <v>31</v>
       </c>
@@ -2194,7 +2197,7 @@
       </c>
       <c r="Q23" s="12"/>
     </row>
-    <row r="24" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A24" s="11" t="s">
         <v>31</v>
       </c>
@@ -2239,7 +2242,7 @@
       </c>
       <c r="Q24" s="12"/>
     </row>
-    <row r="25" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A25" s="11" t="s">
         <v>31</v>
       </c>
@@ -2284,7 +2287,7 @@
       </c>
       <c r="Q25" s="12"/>
     </row>
-    <row r="26" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A26" s="11" t="s">
         <v>31</v>
       </c>
@@ -2329,7 +2332,7 @@
       </c>
       <c r="Q26" s="12"/>
     </row>
-    <row r="27" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A27" s="11" t="s">
         <v>31</v>
       </c>
@@ -2376,7 +2379,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A28" s="11" t="s">
         <v>31</v>
       </c>
@@ -2421,7 +2424,7 @@
       </c>
       <c r="Q28" s="12"/>
     </row>
-    <row r="29" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A29" s="11" t="s">
         <v>31</v>
       </c>
@@ -2468,7 +2471,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A30" s="11" t="s">
         <v>31</v>
       </c>
@@ -2513,7 +2516,7 @@
       </c>
       <c r="Q30" s="12"/>
     </row>
-    <row r="31" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A31" s="11" t="s">
         <v>31</v>
       </c>
@@ -2558,7 +2561,7 @@
       </c>
       <c r="Q31" s="12"/>
     </row>
-    <row r="32" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" s="15" customFormat="1" ht="28.7">
       <c r="A32" s="11" t="s">
         <v>31</v>
       </c>
@@ -2605,7 +2608,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" s="15" customFormat="1">
       <c r="A33" s="11" t="s">
         <v>31</v>
       </c>
@@ -2648,7 +2651,7 @@
       </c>
       <c r="Q33" s="12"/>
     </row>
-    <row r="34" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" s="15" customFormat="1">
       <c r="A34" s="11" t="s">
         <v>31</v>
       </c>
@@ -2691,7 +2694,7 @@
       </c>
       <c r="Q34" s="12"/>
     </row>
-    <row r="35" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" s="15" customFormat="1">
       <c r="A35" s="11" t="s">
         <v>31</v>
       </c>
@@ -2734,7 +2737,7 @@
       </c>
       <c r="Q35" s="12"/>
     </row>
-    <row r="36" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" s="15" customFormat="1">
       <c r="A36" s="11" t="s">
         <v>31</v>
       </c>
@@ -2777,7 +2780,7 @@
       </c>
       <c r="Q36" s="12"/>
     </row>
-    <row r="37" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" s="15" customFormat="1">
       <c r="A37" s="11" t="s">
         <v>31</v>
       </c>
@@ -2822,7 +2825,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" s="15" customFormat="1">
       <c r="A38" s="11" t="s">
         <v>31</v>
       </c>
@@ -2865,7 +2868,7 @@
       </c>
       <c r="Q38" s="12"/>
     </row>
-    <row r="39" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" s="15" customFormat="1">
       <c r="A39" s="11" t="s">
         <v>31</v>
       </c>
@@ -2910,7 +2913,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" s="15" customFormat="1">
       <c r="A40" s="11" t="s">
         <v>31</v>
       </c>
@@ -2953,7 +2956,7 @@
       </c>
       <c r="Q40" s="12"/>
     </row>
-    <row r="41" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" s="15" customFormat="1">
       <c r="A41" s="11" t="s">
         <v>31</v>
       </c>
@@ -2996,7 +2999,7 @@
       </c>
       <c r="Q41" s="12"/>
     </row>
-    <row r="42" spans="1:17" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" s="15" customFormat="1">
       <c r="A42" s="11" t="s">
         <v>31</v>
       </c>
@@ -3134,25 +3137,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D118C320-5B2C-4B05-837B-4243603672BC}">
   <dimension ref="A1:AG99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="3" max="4" width="9" style="10"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.87890625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.29296875" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" customWidth="1"/>
-    <col min="15" max="15" width="52.85546875" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.28515625" customWidth="1"/>
-    <col min="19" max="19" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30.28515625" customWidth="1"/>
-    <col min="21" max="21" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.87890625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1171875" customWidth="1"/>
+    <col min="13" max="13" width="9.703125" customWidth="1"/>
+    <col min="15" max="15" width="52.87890625" customWidth="1"/>
+    <col min="16" max="16" width="12.703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.29296875" customWidth="1"/>
+    <col min="19" max="19" width="9.5859375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.29296875" customWidth="1"/>
+    <col min="21" max="21" width="21.29296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.41015625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="37.700000000000003">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -3250,7 +3253,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="14" customFormat="1" ht="39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" s="14" customFormat="1" ht="37">
       <c r="A2" s="11" t="s">
         <v>31</v>
       </c>
@@ -3328,7 +3331,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
     </row>
-    <row r="3" spans="1:33" s="14" customFormat="1" ht="39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" s="14" customFormat="1" ht="37">
       <c r="A3" s="11" t="s">
         <v>31</v>
       </c>
@@ -3410,7 +3413,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
     </row>
-    <row r="4" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" s="14" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>31</v>
       </c>
@@ -3478,7 +3481,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
     </row>
-    <row r="5" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" s="14" customFormat="1">
       <c r="A5" s="11" t="s">
         <v>31</v>
       </c>
@@ -3546,7 +3549,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
     </row>
-    <row r="6" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" s="14" customFormat="1" ht="25">
       <c r="A6" s="11" t="s">
         <v>31</v>
       </c>
@@ -3626,7 +3629,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
     </row>
-    <row r="7" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" s="14" customFormat="1">
       <c r="A7" s="11" t="s">
         <v>31</v>
       </c>
@@ -3706,7 +3709,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
     </row>
-    <row r="8" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" s="14" customFormat="1" ht="25">
       <c r="A8" s="11" t="s">
         <v>31</v>
       </c>
@@ -3784,7 +3787,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" s="14" customFormat="1" ht="25">
       <c r="A9" s="11" t="s">
         <v>31</v>
       </c>
@@ -3866,7 +3869,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
     </row>
-    <row r="10" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" s="14" customFormat="1" ht="25">
       <c r="A10" s="11" t="s">
         <v>31</v>
       </c>
@@ -3948,7 +3951,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
     </row>
-    <row r="11" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" s="14" customFormat="1" ht="25">
       <c r="A11" s="11" t="s">
         <v>31</v>
       </c>
@@ -4028,7 +4031,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
     </row>
-    <row r="12" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" s="14" customFormat="1">
       <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
@@ -4102,7 +4105,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
     </row>
-    <row r="13" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" s="14" customFormat="1">
       <c r="A13" s="11" t="s">
         <v>31</v>
       </c>
@@ -4176,7 +4179,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
     </row>
-    <row r="14" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" s="14" customFormat="1">
       <c r="A14" s="11" t="s">
         <v>31</v>
       </c>
@@ -4255,7 +4258,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="15" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" s="14" customFormat="1" ht="28.7">
       <c r="A15" s="11" t="s">
         <v>31</v>
       </c>
@@ -4339,7 +4342,7 @@
       <c r="AE15" s="11"/>
       <c r="AF15" s="11"/>
     </row>
-    <row r="16" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" s="14" customFormat="1">
       <c r="A16" s="11" t="s">
         <v>31</v>
       </c>
@@ -4407,7 +4410,7 @@
       <c r="AE16" s="11"/>
       <c r="AF16" s="11"/>
     </row>
-    <row r="17" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" s="14" customFormat="1">
       <c r="A17" s="11" t="s">
         <v>31</v>
       </c>
@@ -4475,7 +4478,7 @@
       <c r="AE17" s="11"/>
       <c r="AF17" s="11"/>
     </row>
-    <row r="18" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" s="14" customFormat="1" ht="28.7">
       <c r="A18" s="11" t="s">
         <v>31</v>
       </c>
@@ -4559,7 +4562,7 @@
       <c r="AE18" s="11"/>
       <c r="AF18" s="11"/>
     </row>
-    <row r="19" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" s="14" customFormat="1">
       <c r="A19" s="11" t="s">
         <v>31</v>
       </c>
@@ -4643,7 +4646,7 @@
       <c r="AE19" s="11"/>
       <c r="AF19" s="11"/>
     </row>
-    <row r="20" spans="1:32" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" s="14" customFormat="1" ht="28.7">
       <c r="A20" s="11" t="s">
         <v>31</v>
       </c>
@@ -4725,7 +4728,7 @@
       <c r="AE20" s="11"/>
       <c r="AF20" s="11"/>
     </row>
-    <row r="21" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A21" s="11" t="s">
         <v>31</v>
       </c>
@@ -4807,7 +4810,7 @@
       <c r="AE21" s="4"/>
       <c r="AF21" s="4"/>
     </row>
-    <row r="22" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" s="14" customFormat="1">
       <c r="A22" s="11" t="s">
         <v>31</v>
       </c>
@@ -4881,7 +4884,7 @@
       <c r="AE22" s="11"/>
       <c r="AF22" s="11"/>
     </row>
-    <row r="23" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" s="14" customFormat="1">
       <c r="A23" s="11" t="s">
         <v>31</v>
       </c>
@@ -4955,7 +4958,7 @@
       <c r="AE23" s="11"/>
       <c r="AF23" s="11"/>
     </row>
-    <row r="24" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" s="14" customFormat="1">
       <c r="A24" s="11" t="s">
         <v>31</v>
       </c>
@@ -5031,7 +5034,7 @@
       <c r="AE24" s="4"/>
       <c r="AF24" s="4"/>
     </row>
-    <row r="25" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A25" s="11" t="s">
         <v>31</v>
       </c>
@@ -5113,7 +5116,7 @@
       <c r="AE25" s="4"/>
       <c r="AF25" s="4"/>
     </row>
-    <row r="26" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" s="14" customFormat="1">
       <c r="A26" s="11" t="s">
         <v>31</v>
       </c>
@@ -5181,7 +5184,7 @@
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
     </row>
-    <row r="27" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" s="14" customFormat="1">
       <c r="A27" s="11" t="s">
         <v>31</v>
       </c>
@@ -5249,7 +5252,7 @@
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
     </row>
-    <row r="28" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A28" s="11" t="s">
         <v>31</v>
       </c>
@@ -5333,7 +5336,7 @@
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
     </row>
-    <row r="29" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" s="14" customFormat="1">
       <c r="A29" s="11" t="s">
         <v>31</v>
       </c>
@@ -5417,7 +5420,7 @@
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
     </row>
-    <row r="30" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A30" s="11" t="s">
         <v>31</v>
       </c>
@@ -5497,7 +5500,7 @@
       <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
     </row>
-    <row r="31" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A31" s="11" t="s">
         <v>31</v>
       </c>
@@ -5579,7 +5582,7 @@
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
     </row>
-    <row r="32" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" s="14" customFormat="1">
       <c r="A32" s="11" t="s">
         <v>31</v>
       </c>
@@ -5653,7 +5656,7 @@
       <c r="AE32" s="4"/>
       <c r="AF32" s="4"/>
     </row>
-    <row r="33" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" s="14" customFormat="1">
       <c r="A33" s="11" t="s">
         <v>31</v>
       </c>
@@ -5727,7 +5730,7 @@
       <c r="AE33" s="4"/>
       <c r="AF33" s="4"/>
     </row>
-    <row r="34" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" s="14" customFormat="1">
       <c r="A34" s="11" t="s">
         <v>31</v>
       </c>
@@ -5803,7 +5806,7 @@
       <c r="AE34" s="4"/>
       <c r="AF34" s="4"/>
     </row>
-    <row r="35" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A35" s="11" t="s">
         <v>31</v>
       </c>
@@ -5887,7 +5890,7 @@
       <c r="AE35" s="4"/>
       <c r="AF35" s="4"/>
     </row>
-    <row r="36" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" s="14" customFormat="1">
       <c r="A36" s="11" t="s">
         <v>31</v>
       </c>
@@ -5955,7 +5958,7 @@
       <c r="AE36" s="4"/>
       <c r="AF36" s="4"/>
     </row>
-    <row r="37" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" s="14" customFormat="1">
       <c r="A37" s="11" t="s">
         <v>31</v>
       </c>
@@ -6023,7 +6026,7 @@
       <c r="AE37" s="4"/>
       <c r="AF37" s="4"/>
     </row>
-    <row r="38" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A38" s="11" t="s">
         <v>31</v>
       </c>
@@ -6107,7 +6110,7 @@
       <c r="AE38" s="4"/>
       <c r="AF38" s="4"/>
     </row>
-    <row r="39" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" s="14" customFormat="1">
       <c r="A39" s="11" t="s">
         <v>31</v>
       </c>
@@ -6191,7 +6194,7 @@
       <c r="AE39" s="4"/>
       <c r="AF39" s="4"/>
     </row>
-    <row r="40" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A40" s="11" t="s">
         <v>31</v>
       </c>
@@ -6271,7 +6274,7 @@
       <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
     </row>
-    <row r="41" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A41" s="11" t="s">
         <v>31</v>
       </c>
@@ -6353,7 +6356,7 @@
       <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
     </row>
-    <row r="42" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" s="14" customFormat="1">
       <c r="A42" s="11" t="s">
         <v>31</v>
       </c>
@@ -6427,7 +6430,7 @@
       <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
     </row>
-    <row r="43" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" s="14" customFormat="1">
       <c r="A43" s="11" t="s">
         <v>31</v>
       </c>
@@ -6501,7 +6504,7 @@
       <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
     </row>
-    <row r="44" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" s="14" customFormat="1">
       <c r="A44" s="11" t="s">
         <v>31</v>
       </c>
@@ -6577,7 +6580,7 @@
       <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
     </row>
-    <row r="45" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A45" s="11" t="s">
         <v>31</v>
       </c>
@@ -6661,7 +6664,7 @@
       <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
     </row>
-    <row r="46" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" s="14" customFormat="1">
       <c r="A46" s="11" t="s">
         <v>31</v>
       </c>
@@ -6729,7 +6732,7 @@
       <c r="AE46" s="4"/>
       <c r="AF46" s="4"/>
     </row>
-    <row r="47" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" s="14" customFormat="1">
       <c r="A47" s="11" t="s">
         <v>31</v>
       </c>
@@ -6797,7 +6800,7 @@
       <c r="AE47" s="4"/>
       <c r="AF47" s="4"/>
     </row>
-    <row r="48" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A48" s="11" t="s">
         <v>31</v>
       </c>
@@ -6881,7 +6884,7 @@
       <c r="AE48" s="4"/>
       <c r="AF48" s="4"/>
     </row>
-    <row r="49" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" s="14" customFormat="1">
       <c r="A49" s="11" t="s">
         <v>31</v>
       </c>
@@ -6965,7 +6968,7 @@
       <c r="AE49" s="4"/>
       <c r="AF49" s="4"/>
     </row>
-    <row r="50" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A50" s="11" t="s">
         <v>31</v>
       </c>
@@ -7045,7 +7048,7 @@
       <c r="AE50" s="4"/>
       <c r="AF50" s="4"/>
     </row>
-    <row r="51" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A51" s="11" t="s">
         <v>31</v>
       </c>
@@ -7127,7 +7130,7 @@
       <c r="AE51" s="4"/>
       <c r="AF51" s="4"/>
     </row>
-    <row r="52" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" s="14" customFormat="1">
       <c r="A52" s="11" t="s">
         <v>31</v>
       </c>
@@ -7201,7 +7204,7 @@
       <c r="AE52" s="4"/>
       <c r="AF52" s="4"/>
     </row>
-    <row r="53" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" s="14" customFormat="1">
       <c r="A53" s="11" t="s">
         <v>31</v>
       </c>
@@ -7275,7 +7278,7 @@
       <c r="AE53" s="4"/>
       <c r="AF53" s="4"/>
     </row>
-    <row r="54" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" s="14" customFormat="1">
       <c r="A54" s="11" t="s">
         <v>31</v>
       </c>
@@ -7351,7 +7354,7 @@
       <c r="AE54" s="11"/>
       <c r="AF54" s="11"/>
     </row>
-    <row r="55" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" s="14" customFormat="1" ht="28.7">
       <c r="A55" s="11" t="s">
         <v>31</v>
       </c>
@@ -7435,7 +7438,7 @@
       <c r="AE55" s="11"/>
       <c r="AF55" s="11"/>
     </row>
-    <row r="56" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" s="14" customFormat="1">
       <c r="A56" s="11" t="s">
         <v>31</v>
       </c>
@@ -7503,7 +7506,7 @@
       <c r="AE56" s="11"/>
       <c r="AF56" s="11"/>
     </row>
-    <row r="57" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" s="14" customFormat="1">
       <c r="A57" s="11" t="s">
         <v>31</v>
       </c>
@@ -7571,7 +7574,7 @@
       <c r="AE57" s="11"/>
       <c r="AF57" s="11"/>
     </row>
-    <row r="58" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" s="14" customFormat="1" ht="28.7">
       <c r="A58" s="11" t="s">
         <v>31</v>
       </c>
@@ -7655,7 +7658,7 @@
       <c r="AE58" s="11"/>
       <c r="AF58" s="11"/>
     </row>
-    <row r="59" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" s="14" customFormat="1">
       <c r="A59" s="11" t="s">
         <v>31</v>
       </c>
@@ -7739,7 +7742,7 @@
       <c r="AE59" s="11"/>
       <c r="AF59" s="11"/>
     </row>
-    <row r="60" spans="1:32" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" s="14" customFormat="1" ht="28.7">
       <c r="A60" s="11" t="s">
         <v>31</v>
       </c>
@@ -7823,7 +7826,7 @@
       <c r="AE60" s="11"/>
       <c r="AF60" s="11"/>
     </row>
-    <row r="61" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" s="14" customFormat="1">
       <c r="A61" s="11" t="s">
         <v>31</v>
       </c>
@@ -7897,7 +7900,7 @@
       <c r="AE61" s="11"/>
       <c r="AF61" s="11"/>
     </row>
-    <row r="62" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" s="14" customFormat="1">
       <c r="A62" s="11" t="s">
         <v>31</v>
       </c>
@@ -7971,7 +7974,7 @@
       <c r="AE62" s="11"/>
       <c r="AF62" s="11"/>
     </row>
-    <row r="63" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" s="14" customFormat="1">
       <c r="A63" s="11" t="s">
         <v>31</v>
       </c>
@@ -8047,7 +8050,7 @@
       <c r="AE63" s="11"/>
       <c r="AF63" s="11"/>
     </row>
-    <row r="64" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" s="14" customFormat="1" ht="28.7">
       <c r="A64" s="11" t="s">
         <v>31</v>
       </c>
@@ -8131,7 +8134,7 @@
       <c r="AE64" s="11"/>
       <c r="AF64" s="11"/>
     </row>
-    <row r="65" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" s="14" customFormat="1">
       <c r="A65" s="11" t="s">
         <v>31</v>
       </c>
@@ -8199,7 +8202,7 @@
       <c r="AE65" s="11"/>
       <c r="AF65" s="11"/>
     </row>
-    <row r="66" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" s="14" customFormat="1">
       <c r="A66" s="11" t="s">
         <v>31</v>
       </c>
@@ -8267,7 +8270,7 @@
       <c r="AE66" s="11"/>
       <c r="AF66" s="11"/>
     </row>
-    <row r="67" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" s="14" customFormat="1" ht="28.7">
       <c r="A67" s="11" t="s">
         <v>31</v>
       </c>
@@ -8351,7 +8354,7 @@
       <c r="AE67" s="11"/>
       <c r="AF67" s="11"/>
     </row>
-    <row r="68" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" s="14" customFormat="1">
       <c r="A68" s="11" t="s">
         <v>31</v>
       </c>
@@ -8435,7 +8438,7 @@
       <c r="AE68" s="11"/>
       <c r="AF68" s="11"/>
     </row>
-    <row r="69" spans="1:32" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" s="14" customFormat="1" ht="28.7">
       <c r="A69" s="11" t="s">
         <v>31</v>
       </c>
@@ -8519,7 +8522,7 @@
       <c r="AE69" s="11"/>
       <c r="AF69" s="11"/>
     </row>
-    <row r="70" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" s="14" customFormat="1">
       <c r="A70" s="11" t="s">
         <v>31</v>
       </c>
@@ -8593,7 +8596,7 @@
       <c r="AE70" s="11"/>
       <c r="AF70" s="11"/>
     </row>
-    <row r="71" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" s="14" customFormat="1">
       <c r="A71" s="11" t="s">
         <v>31</v>
       </c>
@@ -8667,7 +8670,7 @@
       <c r="AE71" s="11"/>
       <c r="AF71" s="11"/>
     </row>
-    <row r="72" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" s="14" customFormat="1">
       <c r="A72" s="11" t="s">
         <v>31</v>
       </c>
@@ -8685,7 +8688,7 @@
         <v>92</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>189</v>
@@ -8743,7 +8746,7 @@
       <c r="AE72" s="11"/>
       <c r="AF72" s="11"/>
     </row>
-    <row r="73" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" s="14" customFormat="1" ht="28.7">
       <c r="A73" s="11" t="s">
         <v>31</v>
       </c>
@@ -8761,7 +8764,7 @@
         <v>92</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H73" s="12" t="s">
         <v>189</v>
@@ -8827,7 +8830,7 @@
       <c r="AE73" s="11"/>
       <c r="AF73" s="11"/>
     </row>
-    <row r="74" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" s="14" customFormat="1">
       <c r="A74" s="11" t="s">
         <v>31</v>
       </c>
@@ -8845,7 +8848,7 @@
         <v>92</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H74" s="12" t="s">
         <v>189</v>
@@ -8895,7 +8898,7 @@
       <c r="AE74" s="11"/>
       <c r="AF74" s="11"/>
     </row>
-    <row r="75" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" s="14" customFormat="1">
       <c r="A75" s="11" t="s">
         <v>31</v>
       </c>
@@ -8913,7 +8916,7 @@
         <v>92</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H75" s="12" t="s">
         <v>189</v>
@@ -8963,7 +8966,7 @@
       <c r="AE75" s="11"/>
       <c r="AF75" s="11"/>
     </row>
-    <row r="76" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" s="14" customFormat="1" ht="28.7">
       <c r="A76" s="11" t="s">
         <v>31</v>
       </c>
@@ -8981,7 +8984,7 @@
         <v>92</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H76" s="12" t="s">
         <v>189</v>
@@ -9047,7 +9050,7 @@
       <c r="AE76" s="11"/>
       <c r="AF76" s="11"/>
     </row>
-    <row r="77" spans="1:32" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" s="14" customFormat="1">
       <c r="A77" s="11" t="s">
         <v>31</v>
       </c>
@@ -9065,7 +9068,7 @@
         <v>92</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H77" s="12" t="s">
         <v>189</v>
@@ -9131,7 +9134,7 @@
       <c r="AE77" s="11"/>
       <c r="AF77" s="11"/>
     </row>
-    <row r="78" spans="1:32" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" s="14" customFormat="1" ht="28.7">
       <c r="A78" s="11" t="s">
         <v>31</v>
       </c>
@@ -9149,7 +9152,7 @@
         <v>92</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H78" s="12" t="s">
         <v>189</v>
@@ -9215,7 +9218,7 @@
       <c r="AE78" s="11"/>
       <c r="AF78" s="11"/>
     </row>
-    <row r="79" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" s="14" customFormat="1">
       <c r="A79" s="11" t="s">
         <v>31</v>
       </c>
@@ -9233,7 +9236,7 @@
         <v>92</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H79" s="12" t="s">
         <v>189</v>
@@ -9289,7 +9292,7 @@
       <c r="AE79" s="11"/>
       <c r="AF79" s="11"/>
     </row>
-    <row r="80" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" s="14" customFormat="1">
       <c r="A80" s="11" t="s">
         <v>31</v>
       </c>
@@ -9307,10 +9310,10 @@
         <v>92</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>111</v>
@@ -9363,7 +9366,7 @@
       <c r="AE80" s="11"/>
       <c r="AF80" s="11"/>
     </row>
-    <row r="81" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" s="14" customFormat="1">
       <c r="A81" s="11" t="s">
         <v>31</v>
       </c>
@@ -9439,7 +9442,7 @@
       <c r="AE81" s="4"/>
       <c r="AF81" s="4"/>
     </row>
-    <row r="82" spans="1:33" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" s="14" customFormat="1" ht="25">
       <c r="A82" s="11" t="s">
         <v>31</v>
       </c>
@@ -9523,7 +9526,7 @@
       <c r="AE82" s="4"/>
       <c r="AF82" s="4"/>
     </row>
-    <row r="83" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" s="14" customFormat="1">
       <c r="A83" s="11" t="s">
         <v>31</v>
       </c>
@@ -9591,7 +9594,7 @@
       <c r="AE83" s="4"/>
       <c r="AF83" s="4"/>
     </row>
-    <row r="84" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" s="14" customFormat="1">
       <c r="A84" s="11" t="s">
         <v>31</v>
       </c>
@@ -9659,7 +9662,7 @@
       <c r="AE84" s="4"/>
       <c r="AF84" s="4"/>
     </row>
-    <row r="85" spans="1:33" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" s="14" customFormat="1" ht="25">
       <c r="A85" s="11" t="s">
         <v>31</v>
       </c>
@@ -9743,7 +9746,7 @@
       <c r="AE85" s="4"/>
       <c r="AF85" s="4"/>
     </row>
-    <row r="86" spans="1:33" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" s="14" customFormat="1">
       <c r="A86" s="11" t="s">
         <v>31</v>
       </c>
@@ -9827,7 +9830,7 @@
       <c r="AE86" s="4"/>
       <c r="AF86" s="4"/>
     </row>
-    <row r="87" spans="1:33" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" s="14" customFormat="1" ht="25">
       <c r="A87" s="11" t="s">
         <v>31</v>
       </c>
@@ -9911,7 +9914,7 @@
       <c r="AE87" s="4"/>
       <c r="AF87" s="4"/>
     </row>
-    <row r="88" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" s="14" customFormat="1">
       <c r="A88" s="11" t="s">
         <v>31</v>
       </c>
@@ -9985,7 +9988,7 @@
       <c r="AE88" s="4"/>
       <c r="AF88" s="4"/>
     </row>
-    <row r="89" spans="1:33" s="14" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" s="14" customFormat="1" ht="21" customHeight="1">
       <c r="A89" s="11" t="s">
         <v>31</v>
       </c>
@@ -10059,7 +10062,7 @@
       <c r="AE89" s="4"/>
       <c r="AF89" s="4"/>
     </row>
-    <row r="90" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" s="14" customFormat="1">
       <c r="A90" s="11" t="s">
         <v>31</v>
       </c>
@@ -10138,7 +10141,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="91" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" s="14" customFormat="1" ht="28.7">
       <c r="A91" s="11" t="s">
         <v>31</v>
       </c>
@@ -10222,7 +10225,7 @@
       <c r="AE91" s="11"/>
       <c r="AF91" s="11"/>
     </row>
-    <row r="92" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" s="14" customFormat="1">
       <c r="A92" s="11" t="s">
         <v>31</v>
       </c>
@@ -10290,7 +10293,7 @@
       <c r="AE92" s="11"/>
       <c r="AF92" s="11"/>
     </row>
-    <row r="93" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" s="14" customFormat="1">
       <c r="A93" s="11" t="s">
         <v>31</v>
       </c>
@@ -10358,7 +10361,7 @@
       <c r="AE93" s="11"/>
       <c r="AF93" s="11"/>
     </row>
-    <row r="94" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" s="14" customFormat="1" ht="28.7">
       <c r="A94" s="11" t="s">
         <v>31</v>
       </c>
@@ -10442,7 +10445,7 @@
       <c r="AE94" s="11"/>
       <c r="AF94" s="11"/>
     </row>
-    <row r="95" spans="1:33" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" s="14" customFormat="1">
       <c r="A95" s="11" t="s">
         <v>31</v>
       </c>
@@ -10526,7 +10529,7 @@
       <c r="AE95" s="11"/>
       <c r="AF95" s="11"/>
     </row>
-    <row r="96" spans="1:33" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" s="14" customFormat="1" ht="28.7">
       <c r="A96" s="11" t="s">
         <v>31</v>
       </c>
@@ -10608,7 +10611,7 @@
       <c r="AE96" s="11"/>
       <c r="AF96" s="11"/>
     </row>
-    <row r="97" spans="1:32" s="14" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" s="14" customFormat="1" ht="25">
       <c r="A97" s="11" t="s">
         <v>31</v>
       </c>
@@ -10690,7 +10693,7 @@
       <c r="AE97" s="4"/>
       <c r="AF97" s="4"/>
     </row>
-    <row r="98" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" s="14" customFormat="1">
       <c r="A98" s="11" t="s">
         <v>31</v>
       </c>
@@ -10764,7 +10767,7 @@
       <c r="AE98" s="11"/>
       <c r="AF98" s="11"/>
     </row>
-    <row r="99" spans="1:32" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" s="14" customFormat="1">
       <c r="A99" s="11" t="s">
         <v>31</v>
       </c>
@@ -16440,6 +16443,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Description0 xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">Data and Metadata documentation will explain structure and content any QC manipulations that have been done to the data.</Description0>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EA3DD6FD0640724CAC6A104AA4040E53" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="866aaee467307fab2f51bbdbaaea79d8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3dc215b4-4765-4137-95ef-e24fb8216673" xmlns:ns3="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636a025d234e12dfc0e20f1263040641" ns2:_="" ns3:_="">
     <xsd:import namespace="3dc215b4-4765-4137-95ef-e24fb8216673"/>
@@ -16696,28 +16720,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72C26AEA-38B4-45B2-94FF-5972E3017E52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3dc215b4-4765-4137-95ef-e24fb8216673"/>
+    <ds:schemaRef ds:uri="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Description0 xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">Data and Metadata documentation will explain structure and content any QC manipulations that have been done to the data.</Description0>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62FA68FA-8C71-4E93-80BA-49A20AA62094}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39409D45-3830-4E57-BD4D-A5503E0F1185}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16736,25 +16758,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62FA68FA-8C71-4E93-80BA-49A20AA62094}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72C26AEA-38B4-45B2-94FF-5972E3017E52}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3dc215b4-4765-4137-95ef-e24fb8216673"/>
-    <ds:schemaRef ds:uri="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{078244a1-de67-4c9e-9088-986d7f110a37}" enabled="0" method="" siteId="{078244a1-de67-4c9e-9088-986d7f110a37}" removed="1"/>
